--- a/Plantillas/PlantillaDocumentaciónDiagramaSecuencia.xlsx
+++ b/Plantillas/PlantillaDocumentaciónDiagramaSecuencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28706"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciana\Documents\Estructura\1. Artefactos proyecto\1.2. Artefactos técnicos\1.2.2. Diseño detallado\1.2.2.4. Diagrama de secuencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:101_{AF34198A-7A13-472F-BDF2-5C3C673706B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A2ED8CA-F6C5-40DB-8EFC-FA4FD06D1509}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:101_{AF34198A-7A13-472F-BDF2-5C3C673706B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CBF6160-CA74-4B76-A67D-C5C3A4E7B06B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{89DBD8A5-DC87-4190-9617-E764C549D606}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="1" xr2:uid="{89DBD8A5-DC87-4190-9617-E764C549D606}"/>
   </bookViews>
   <sheets>
     <sheet name="Diagrama Secuencia" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>En esta hoja se ubica la imagen del modelo, asegurando que sea clara y legible</t>
   </si>
@@ -69,88 +69,106 @@
     <t>Descripción</t>
   </si>
   <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Representa al actor principal que interactúa con el sistema. En este caso, es el usuario que se registra, envía una solicitud de cotización y recibe las respuestas del sistema.</t>
+    <t>Usuario</t>
+  </si>
+  <si>
+    <t>Representa al usuario autenticado (Dueño o Colaborador) que interactúa con la interfaz. Es el encargado de enviar los datos de negocio (como títulos, fechas y productos) y recibir las confirmaciones o errores del sistema.</t>
+  </si>
+  <si>
+    <t>API (Controller)</t>
+  </si>
+  <si>
+    <t>Actúa como la puerta de entrada técnica. Su función es recibir la petición HTTP, validar el formato de los datos a través de DTOs y aplicar Middlewares de seguridad antes de delegar la ejecución a la lógica de negocio.</t>
+  </si>
+  <si>
+    <t>Use Case</t>
+  </si>
+  <si>
+    <t>Es el corazón del sistema donde residen las Reglas de Negocio. Se encarga de orquestar el flujo: valida límites de suscripciones, consulta estados de otros módulos y asegura que la operación cumpla con las políticas de la aplicación antes de persistir.</t>
+  </si>
+  <si>
+    <t>Repository (Data)</t>
+  </si>
+  <si>
+    <t>Se encarga exclusivamente del acceso a la persistencia a través de TypeORM. Su responsabilidad es transformar los objetos de negocio en registros de la base de datos, garantizando que la información se almacene de forma íntegra y segura.</t>
+  </si>
+  <si>
+    <t>Interacción</t>
+  </si>
+  <si>
+    <t>Acción</t>
+  </si>
+  <si>
+    <t>Origen</t>
+  </si>
+  <si>
+    <t>Destino</t>
+  </si>
+  <si>
+    <t>1. Enviar Solicitud</t>
   </si>
   <si>
     <t>API</t>
   </si>
   <si>
-    <t>Punto de entrada del sistema que gestiona las solicitudes del cliente. Se encarga de recibir la solicitud, devolver el formulario correspondiente y enviar los datos al componente de negocio para su validación y procesamiento.</t>
-  </si>
-  <si>
-    <t>Business</t>
-  </si>
-  <si>
-    <t>Componente encargado de la lógica principal del negocio. Valida los datos recibidos, maneja excepciones, verifica la existencia de la solicitud y finalmente envía la respuesta correspondiente. Además, genera la solicitud de cotización basada en la información del cliente.</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Se encarga del acceso a la fuente de datos. Realiza la verificación de registros, almacena la información de la solicitud de cotización y envía una respuesta indicando el resultado del proceso.</t>
-  </si>
-  <si>
-    <t>Interacción</t>
-  </si>
-  <si>
-    <t>Acción</t>
-  </si>
-  <si>
-    <t>Origen</t>
-  </si>
-  <si>
-    <t>Destino</t>
-  </si>
-  <si>
-    <t>1. registrarse</t>
-  </si>
-  <si>
-    <t>El cliente inicia el proceso de registro enviando una solicitud de registro a la API.</t>
-  </si>
-  <si>
-    <t>2. formulario</t>
-  </si>
-  <si>
-    <t>La API responde enviando un formulario que el cliente debe completar.</t>
-  </si>
-  <si>
-    <t>3. enviarSolicitudCotización</t>
-  </si>
-  <si>
-    <t>El cliente completa el formulario y lo envía a la API como una solicitud de cotización.</t>
-  </si>
-  <si>
-    <t>4. validarDatosYExcepciones</t>
-  </si>
-  <si>
-    <t>La API reenvía la solicitud de cotización al módulo de negocio para que valide los datos y gestione posibles excepciones.</t>
-  </si>
-  <si>
-    <t>5. verificarExistenciaSolicitud</t>
-  </si>
-  <si>
-    <t>El módulo de negocio verifica en la base de datos si existe una solicitud de cotización previa para el cliente.</t>
-  </si>
-  <si>
-    <t>6. mensajeRespuesta</t>
-  </si>
-  <si>
-    <t>La base de datos responde con el resultado de la verificación, indicando si existe o no una solicitud previa.</t>
-  </si>
-  <si>
-    <t>7. mensajeEnvioExitoso</t>
-  </si>
-  <si>
-    <t>El módulo de negocio confirma que la solicitud de cotización ha sido procesada correctamente y envía un mensaje de éxito a la API.</t>
-  </si>
-  <si>
-    <t>8. mensajeEnvioExitoso</t>
-  </si>
-  <si>
-    <t>La API informa al cliente que su solicitud fue enviada con éxito.</t>
+    <t>El usuario envía el formulario con los datos de la solicitud y productos (DTO).</t>
+  </si>
+  <si>
+    <t>2. Validar Sesión</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Se verifica que el token JWT sea válido y se extrae el ID del usuario/dueño.</t>
+  </si>
+  <si>
+    <t>3. Ejecutar Proceso</t>
+  </si>
+  <si>
+    <t>Se transfiere el DTO y la sesión al Caso de Uso </t>
+  </si>
+  <si>
+    <t>4. Consultar Perfil</t>
+  </si>
+  <si>
+    <t>Se busca la información del usuario para obtener su planId y fecha de inicio</t>
+  </si>
+  <si>
+    <t>5. Verificar Plan</t>
+  </si>
+  <si>
+    <t>Se obtienen los límites técnicos del plan contratado (ej: Máximo 10 solicitudes).</t>
+  </si>
+  <si>
+    <t>6. Calcular Consumo</t>
+  </si>
+  <si>
+    <t>Se cuenta cuántas solicitudes ha creado el usuario en el periodo actual.</t>
+  </si>
+  <si>
+    <t>7. Validar Límites</t>
+  </si>
+  <si>
+    <t>Se comprueba si el usuario aún tiene cupo disponible según su plan.</t>
+  </si>
+  <si>
+    <t>8. Persistir Datos</t>
+  </si>
+  <si>
+    <t>Si hay cupo, se crea la entidad y se guarda en la base de datos (TypeORM).</t>
+  </si>
+  <si>
+    <t>9. Confirmar Éxito</t>
+  </si>
+  <si>
+    <t>La base de datos confirma el almacenamiento exitoso y asigna el ID único.</t>
+  </si>
+  <si>
+    <t>10. Respuesta Final</t>
+  </si>
+  <si>
+    <t>El sistema retorna la solicitud creada con estado 201 (Created).</t>
   </si>
 </sst>
 </file>
@@ -456,6 +474,15 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -482,15 +509,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,21 +539,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Imagen 5">
+        <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D4BB650-A033-3390-3D11-C0FED48301C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93B983E1-0F5C-7E5B-0A92-D20F2E3F71C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -551,8 +569,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="533400"/>
-          <a:ext cx="9696450" cy="5962650"/>
+          <a:off x="0" y="581025"/>
+          <a:ext cx="13601700" cy="8372475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -884,11 +902,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9711F7B-CB2F-41BF-88AA-A7043145A5E1}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.85546875" style="3"/>
+    <col min="2" max="3" width="16.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="65" style="8" customWidth="1"/>
     <col min="5" max="16384" width="10.85546875" style="3"/>
   </cols>
@@ -897,89 +915,89 @@
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="19"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
     </row>
     <row r="3" spans="1:4" ht="34.5" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="26"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
-    </row>
-    <row r="6" spans="1:4" ht="31.5" customHeight="1">
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+    </row>
+    <row r="6" spans="1:4" ht="50.25" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-    </row>
-    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:4" ht="49.5" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="20"/>
     </row>
     <row r="8" spans="1:4" ht="47.25" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-    </row>
-    <row r="9" spans="1:4" ht="37.5" customHeight="1">
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+    </row>
+    <row r="9" spans="1:4" ht="51.75" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="1:4" s="7" customFormat="1">
       <c r="A10" s="15" t="s">
@@ -1011,57 +1029,57 @@
         <v>10</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30.75">
       <c r="A13" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30.75">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="45.75">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30.75">
       <c r="A15" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="45.75">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30.75">
       <c r="A16" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>14</v>
@@ -1070,50 +1088,96 @@
         <v>16</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="45.75">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="D17" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="45.75">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30.75">
       <c r="A19" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>37</v>
-      </c>
+      <c r="D21" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="D30" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1134,19 +1198,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="36cf0646-7300-4608-bcc3-e29ed014863a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="734bc881-a844-4d86-9741-49f87248cc41" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001945CC36234B18439988D70FCB761011" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="49d1d5a573ca54dccef2d71c1bfe4d0c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36cf0646-7300-4608-bcc3-e29ed014863a" xmlns:ns3="734bc881-a844-4d86-9741-49f87248cc41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb428a4efaeddf2ef8bccbe6d8f13bc5" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001945CC36234B18439988D70FCB761011" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8ca733e0ec3c0df6e34813901e7a3ca5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36cf0646-7300-4608-bcc3-e29ed014863a" xmlns:ns3="734bc881-a844-4d86-9741-49f87248cc41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aed9a3083501fe1d9ea761da13b3b1bf" ns2:_="" ns3:_="">
     <xsd:import namespace="36cf0646-7300-4608-bcc3-e29ed014863a"/>
     <xsd:import namespace="734bc881-a844-4d86-9741-49f87248cc41"/>
     <xsd:element name="properties">
@@ -1339,7 +1392,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1348,16 +1401,27 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="36cf0646-7300-4608-bcc3-e29ed014863a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="734bc881-a844-4d86-9741-49f87248cc41" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85E4EF7A-AECA-43D9-8B32-DF999D0441BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9549D56D-E67A-4A4C-9BBB-155ED32BBDFB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61A8E8FA-A7E2-4B27-AA5C-4D97C379BAC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4143ED4-0227-43FF-89AD-B06FDED30A23}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4143ED4-0227-43FF-89AD-B06FDED30A23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85E4EF7A-AECA-43D9-8B32-DF999D0441BF}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
